--- a/artfynd/S 487-2025 artfynd.xlsx
+++ b/artfynd/S 487-2025 artfynd.xlsx
@@ -828,7 +828,7 @@
         <v>524403</v>
       </c>
       <c r="R3" t="n">
-        <v>6935551</v>
+        <v>6935552</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/S 487-2025 artfynd.xlsx
+++ b/artfynd/S 487-2025 artfynd.xlsx
@@ -828,7 +828,7 @@
         <v>524403</v>
       </c>
       <c r="R3" t="n">
-        <v>6935552</v>
+        <v>6935551</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/S 487-2025 artfynd.xlsx
+++ b/artfynd/S 487-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539846</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134455588</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539848</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539855</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1224,6 +1249,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539867</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134453639</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134455807</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456213</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1612,6 +1657,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456275</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1709,6 +1759,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134453790</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1806,6 +1861,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134453823</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1921,6 +1981,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539860</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2031,6 +2096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539849</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2146,6 +2216,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539865</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2248,6 +2323,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134455067</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2345,6 +2425,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134454558</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2455,6 +2540,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539861</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2570,6 +2660,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539856</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2680,6 +2775,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539863</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2777,6 +2877,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134455935</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2874,6 +2979,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456561</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2971,6 +3081,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457204</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3081,6 +3196,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539866</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3178,6 +3298,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134453822</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3275,6 +3400,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134455033</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3372,6 +3502,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456018</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3469,6 +3604,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456075</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3566,6 +3706,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134455505</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3663,6 +3808,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134454814</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3769,6 +3919,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539850</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3875,6 +4030,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539853</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3981,6 +4141,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539858</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4087,6 +4252,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539862</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4184,6 +4354,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134454340</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4281,6 +4456,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134454805</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4378,6 +4558,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134454869</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4475,6 +4660,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134455331</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4572,6 +4762,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456005</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4674,6 +4869,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456885</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4771,6 +4971,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457188</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4868,6 +5073,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134454113</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4965,6 +5175,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134454155</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5062,6 +5277,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134455344</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5159,6 +5379,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134455444</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5256,6 +5481,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456975</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5353,6 +5583,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134454445</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5450,6 +5685,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134454498</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5547,6 +5787,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134454480</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5644,6 +5889,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134454539</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5741,6 +5991,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457193</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5856,8 +6111,66 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539854</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>